--- a/Deliverables/Control_Board/BOM/Control_Board_BOM (500 Boards).xlsx
+++ b/Deliverables/Control_Board/BOM/Control_Board_BOM (500 Boards).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Control_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DEE847-1B02-4659-B3C6-F108D0456207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370284ED-8F79-40EB-8105-287A2A756DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="188">
   <si>
     <t>Component list</t>
   </si>
@@ -574,9 +574,6 @@
 </t>
   </si>
   <si>
-    <t>Need Quote from Custom Supplier</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total Component Cost </t>
   </si>
   <si>
@@ -593,6 +590,15 @@
   </si>
   <si>
     <t xml:space="preserve">1x40 pins Header 5 PCS per Lot </t>
+  </si>
+  <si>
+    <t>Custom Supplier</t>
+  </si>
+  <si>
+    <t>Karen Quotes</t>
+  </si>
+  <si>
+    <t>Already Purchas From Client Side</t>
   </si>
 </sst>
 </file>
@@ -1180,7 +1186,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1288,30 +1294,6 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1398,15 +1380,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1447,6 +1420,69 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="27" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1457,105 +1493,81 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="27" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1907,13 +1919,15 @@
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.42578125" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.42578125" customWidth="1"/>
+    <col min="7" max="7" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="29.42578125" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="25.85546875" customWidth="1"/>
     <col min="18" max="18" width="29.42578125" customWidth="1"/>
@@ -1931,20 +1945,20 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="44"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="117"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
-      <c r="C2" s="72"/>
+      <c r="C2" s="64"/>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
@@ -1969,7 +1983,7 @@
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
-      <c r="C3" s="73"/>
+      <c r="C3" s="65"/>
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
@@ -1989,12 +2003,12 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="45"/>
+      <c r="S3" s="118"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
-      <c r="C4" s="73"/>
+      <c r="C4" s="65"/>
       <c r="D4" s="13" t="s">
         <v>2</v>
       </c>
@@ -2014,12 +2028,12 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="46"/>
+      <c r="S4" s="119"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
-      <c r="C5" s="73"/>
+      <c r="C5" s="65"/>
       <c r="D5" s="13" t="s">
         <v>3</v>
       </c>
@@ -2039,12 +2053,12 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="46"/>
+      <c r="S5" s="119"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
-      <c r="C6" s="74"/>
+      <c r="C6" s="66"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
@@ -2060,12 +2074,12 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="46"/>
+      <c r="S6" s="119"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
-      <c r="C7" s="75"/>
+      <c r="C7" s="67"/>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
@@ -2081,12 +2095,12 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="46"/>
+      <c r="S7" s="119"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="76"/>
+      <c r="C8" s="68"/>
       <c r="D8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="29"/>
@@ -2102,7 +2116,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="46"/>
+      <c r="S8" s="119"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2127,7 +2141,7 @@
       <c r="H9" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="I9" s="105" t="s">
+      <c r="I9" s="89" t="s">
         <v>94</v>
       </c>
       <c r="J9" s="30" t="s">
@@ -2142,7 +2156,7 @@
       <c r="M9" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="N9" s="105" t="s">
+      <c r="N9" s="89" t="s">
         <v>129</v>
       </c>
       <c r="O9" s="30" t="s">
@@ -2167,55 +2181,55 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="124" t="s">
         <v>151</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="52" t="s">
+      <c r="E10" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="51" t="s">
+      <c r="F10" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="G10" s="52" t="s">
+      <c r="G10" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="H10" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I10" s="69" t="s">
+      <c r="H10" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I10" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="J10" s="51" t="s">
+      <c r="J10" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="K10" s="53" t="s">
+      <c r="K10" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="L10" s="52">
+      <c r="L10" s="44">
         <v>4</v>
       </c>
-      <c r="M10" s="51">
+      <c r="M10" s="43">
         <f>L10*500</f>
         <v>2000</v>
       </c>
-      <c r="N10" s="69">
+      <c r="N10" s="61">
         <v>2020</v>
       </c>
-      <c r="O10" s="68" t="s">
+      <c r="O10" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="P10" s="71">
+      <c r="P10" s="63">
         <v>9.2799999999999994E-2</v>
       </c>
-      <c r="Q10" s="63">
+      <c r="Q10" s="55">
         <f>P10*N10</f>
         <v>187.45599999999999</v>
       </c>
-      <c r="R10" s="53"/>
-      <c r="S10" s="54"/>
+      <c r="R10" s="45"/>
+      <c r="S10" s="46"/>
     </row>
     <row r="11" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -2223,53 +2237,53 @@
         <f t="shared" ref="B11:B35" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="80"/>
-      <c r="D11" s="55" t="s">
+      <c r="C11" s="125"/>
+      <c r="D11" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="56" t="s">
+      <c r="E11" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="55" t="s">
+      <c r="F11" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="56" t="s">
+      <c r="G11" s="48" t="s">
         <v>81</v>
       </c>
-      <c r="H11" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="I11" s="70" t="s">
+      <c r="H11" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="I11" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="J11" s="55" t="s">
+      <c r="J11" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="K11" s="58" t="s">
+      <c r="K11" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="L11" s="56">
+      <c r="L11" s="48">
         <v>24</v>
       </c>
-      <c r="M11" s="57">
+      <c r="M11" s="49">
         <f t="shared" ref="M11:M36" si="1">L11*500</f>
         <v>12000</v>
       </c>
-      <c r="N11" s="70">
+      <c r="N11" s="62">
         <v>12100</v>
       </c>
-      <c r="O11" s="62" t="s">
+      <c r="O11" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="P11" s="86">
+      <c r="P11" s="75">
         <v>4.4000000000000003E-3</v>
       </c>
-      <c r="Q11" s="64">
+      <c r="Q11" s="56">
         <f t="shared" ref="Q11:Q36" si="2">P11*N11</f>
         <v>53.24</v>
       </c>
-      <c r="R11" s="58"/>
-      <c r="S11" s="59"/>
+      <c r="R11" s="50"/>
+      <c r="S11" s="51"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -2277,53 +2291,53 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="80"/>
-      <c r="D12" s="51" t="s">
+      <c r="C12" s="125"/>
+      <c r="D12" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="51" t="s">
+      <c r="F12" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="G12" s="52" t="s">
+      <c r="G12" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="H12" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I12" s="69" t="s">
+      <c r="H12" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I12" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="J12" s="51" t="s">
+      <c r="J12" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="K12" s="53" t="s">
+      <c r="K12" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="L12" s="52">
+      <c r="L12" s="44">
         <v>1</v>
       </c>
-      <c r="M12" s="51">
+      <c r="M12" s="43">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N12" s="69">
+      <c r="N12" s="61">
         <v>510</v>
       </c>
-      <c r="O12" s="68" t="s">
+      <c r="O12" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="P12" s="71">
+      <c r="P12" s="63">
         <v>6.4199999999999993E-2</v>
       </c>
-      <c r="Q12" s="63">
+      <c r="Q12" s="55">
         <f t="shared" si="2"/>
         <v>32.741999999999997</v>
       </c>
-      <c r="R12" s="53"/>
-      <c r="S12" s="60"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="52"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
@@ -2331,53 +2345,53 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="80"/>
-      <c r="D13" s="55" t="s">
+      <c r="C13" s="125"/>
+      <c r="D13" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="56" t="s">
+      <c r="E13" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="55" t="s">
+      <c r="F13" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="56" t="s">
+      <c r="G13" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="H13" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="I13" s="70" t="s">
+      <c r="H13" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="J13" s="55" t="s">
+      <c r="J13" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="K13" s="58" t="s">
+      <c r="K13" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="L13" s="56">
+      <c r="L13" s="48">
         <v>3</v>
       </c>
-      <c r="M13" s="57">
+      <c r="M13" s="49">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="N13" s="70">
+      <c r="N13" s="62">
         <v>1520</v>
       </c>
-      <c r="O13" s="62" t="s">
+      <c r="O13" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="P13" s="86">
+      <c r="P13" s="75">
         <v>1.4E-2</v>
       </c>
-      <c r="Q13" s="64">
+      <c r="Q13" s="56">
         <f t="shared" si="2"/>
         <v>21.28</v>
       </c>
-      <c r="R13" s="58"/>
-      <c r="S13" s="59"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="51"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -2385,53 +2399,53 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="80"/>
-      <c r="D14" s="51" t="s">
+      <c r="C14" s="125"/>
+      <c r="D14" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="52" t="s">
+      <c r="E14" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="51" t="s">
+      <c r="F14" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="66" t="s">
+      <c r="G14" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="H14" s="51" t="s">
+      <c r="H14" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="I14" s="69" t="s">
+      <c r="I14" s="61" t="s">
         <v>98</v>
       </c>
-      <c r="J14" s="51" t="s">
+      <c r="J14" s="43" t="s">
         <v>140</v>
       </c>
-      <c r="K14" s="53" t="s">
+      <c r="K14" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="L14" s="52">
+      <c r="L14" s="44">
         <v>4</v>
       </c>
-      <c r="M14" s="51">
+      <c r="M14" s="43">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
-      <c r="N14" s="69">
+      <c r="N14" s="61">
         <v>2100</v>
       </c>
-      <c r="O14" s="117" t="s">
+      <c r="O14" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="P14" s="71">
+      <c r="P14" s="63">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="Q14" s="63">
+      <c r="Q14" s="55">
         <f t="shared" si="2"/>
         <v>6.51</v>
       </c>
-      <c r="R14" s="53"/>
-      <c r="S14" s="60"/>
+      <c r="R14" s="45"/>
+      <c r="S14" s="52"/>
     </row>
     <row r="15" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
@@ -2439,57 +2453,57 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="79" t="s">
+      <c r="C15" s="124" t="s">
         <v>152</v>
       </c>
-      <c r="D15" s="55" t="s">
+      <c r="D15" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="56" t="s">
+      <c r="E15" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="55" t="s">
+      <c r="F15" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="84" t="s">
+      <c r="G15" s="73" t="s">
         <v>117</v>
       </c>
-      <c r="H15" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="I15" s="70" t="s">
+      <c r="H15" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="I15" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="J15" s="65" t="s">
-        <v>183</v>
-      </c>
-      <c r="K15" s="107" t="s">
+      <c r="J15" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K15" s="91" t="s">
         <v>162</v>
       </c>
-      <c r="L15" s="56">
+      <c r="L15" s="48">
         <v>1</v>
       </c>
-      <c r="M15" s="57">
+      <c r="M15" s="49">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N15" s="113">
+      <c r="N15" s="114">
         <v>140</v>
       </c>
-      <c r="O15" s="118" t="s">
+      <c r="O15" s="127" t="s">
         <v>175</v>
       </c>
-      <c r="P15" s="115">
+      <c r="P15" s="110">
         <v>0.41</v>
       </c>
-      <c r="Q15" s="103">
+      <c r="Q15" s="112">
         <f t="shared" si="2"/>
         <v>57.4</v>
       </c>
-      <c r="R15" s="128" t="s">
-        <v>185</v>
-      </c>
-      <c r="S15" s="59"/>
+      <c r="R15" s="108" t="s">
+        <v>184</v>
+      </c>
+      <c r="S15" s="51"/>
     </row>
     <row r="16" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
@@ -2497,44 +2511,44 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="80"/>
-      <c r="D16" s="51" t="s">
+      <c r="C16" s="125"/>
+      <c r="D16" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="E16" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="51" t="s">
+      <c r="F16" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="G16" s="102" t="s">
+      <c r="G16" s="88" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I16" s="69" t="s">
+      <c r="H16" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I16" s="61" t="s">
         <v>99</v>
       </c>
-      <c r="J16" s="67" t="s">
-        <v>184</v>
-      </c>
-      <c r="K16" s="108" t="s">
+      <c r="J16" s="59" t="s">
+        <v>183</v>
+      </c>
+      <c r="K16" s="92" t="s">
         <v>162</v>
       </c>
-      <c r="L16" s="52">
+      <c r="L16" s="44">
         <v>1</v>
       </c>
-      <c r="M16" s="51">
+      <c r="M16" s="43">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N16" s="114"/>
-      <c r="O16" s="119"/>
-      <c r="P16" s="116"/>
-      <c r="Q16" s="104"/>
-      <c r="R16" s="129"/>
-      <c r="S16" s="60"/>
+      <c r="N16" s="115"/>
+      <c r="O16" s="128"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="113"/>
+      <c r="R16" s="109"/>
+      <c r="S16" s="52"/>
     </row>
     <row r="17" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
@@ -2542,53 +2556,53 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="81"/>
-      <c r="D17" s="55" t="s">
+      <c r="C17" s="126"/>
+      <c r="D17" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="56" t="s">
+      <c r="E17" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="F17" s="55" t="s">
+      <c r="F17" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="G17" s="92" t="s">
+      <c r="G17" s="81" t="s">
         <v>178</v>
       </c>
-      <c r="H17" s="56" t="s">
+      <c r="H17" s="48" t="s">
         <v>177</v>
       </c>
-      <c r="I17" s="70" t="s">
+      <c r="I17" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="J17" s="65" t="s">
+      <c r="J17" s="57" t="s">
         <v>162</v>
       </c>
-      <c r="K17" s="107" t="s">
+      <c r="K17" s="91" t="s">
         <v>162</v>
       </c>
-      <c r="L17" s="56">
+      <c r="L17" s="48">
         <v>1</v>
       </c>
-      <c r="M17" s="57">
+      <c r="M17" s="49">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N17" s="70">
+      <c r="N17" s="62">
         <v>510</v>
       </c>
-      <c r="O17" s="94" t="s">
+      <c r="O17" s="83" t="s">
         <v>175</v>
       </c>
-      <c r="P17" s="86">
+      <c r="P17" s="75">
         <v>0.13200000000000001</v>
       </c>
-      <c r="Q17" s="64">
+      <c r="Q17" s="56">
         <f t="shared" si="2"/>
         <v>67.320000000000007</v>
       </c>
-      <c r="R17" s="58"/>
-      <c r="S17" s="59"/>
+      <c r="R17" s="50"/>
+      <c r="S17" s="51"/>
     </row>
     <row r="18" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -2596,55 +2610,55 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="79" t="s">
+      <c r="C18" s="124" t="s">
         <v>153</v>
       </c>
-      <c r="D18" s="51" t="s">
+      <c r="D18" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="52" t="s">
+      <c r="E18" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="87" t="s">
+      <c r="F18" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G18" s="53" t="s">
+      <c r="G18" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="H18" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I18" s="69" t="s">
+      <c r="H18" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I18" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="J18" s="51" t="s">
+      <c r="J18" s="43" t="s">
         <v>161</v>
       </c>
-      <c r="K18" s="108" t="s">
+      <c r="K18" s="92" t="s">
         <v>162</v>
       </c>
-      <c r="L18" s="52">
+      <c r="L18" s="44">
         <v>5</v>
       </c>
-      <c r="M18" s="51">
+      <c r="M18" s="43">
         <f t="shared" si="1"/>
         <v>2500</v>
       </c>
-      <c r="N18" s="69">
+      <c r="N18" s="61">
         <v>2550</v>
       </c>
-      <c r="O18" s="120" t="s">
+      <c r="O18" s="97" t="s">
         <v>136</v>
       </c>
-      <c r="P18" s="71">
+      <c r="P18" s="63">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="Q18" s="63">
+      <c r="Q18" s="55">
         <f t="shared" si="2"/>
         <v>17.594999999999999</v>
       </c>
-      <c r="R18" s="53"/>
-      <c r="S18" s="60"/>
+      <c r="R18" s="45"/>
+      <c r="S18" s="52"/>
     </row>
     <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
@@ -2652,53 +2666,53 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="80"/>
-      <c r="D19" s="55" t="s">
+      <c r="C19" s="125"/>
+      <c r="D19" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="56" t="s">
+      <c r="E19" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="55" t="s">
+      <c r="F19" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="88" t="s">
+      <c r="G19" s="77" t="s">
         <v>163</v>
       </c>
-      <c r="H19" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="I19" s="70" t="s">
+      <c r="H19" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="I19" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="J19" s="55" t="s">
+      <c r="J19" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="K19" s="107" t="s">
+      <c r="K19" s="91" t="s">
         <v>162</v>
       </c>
-      <c r="L19" s="56">
+      <c r="L19" s="48">
         <v>1</v>
       </c>
-      <c r="M19" s="57">
+      <c r="M19" s="49">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N19" s="70">
+      <c r="N19" s="62">
         <v>520</v>
       </c>
-      <c r="O19" s="121" t="s">
+      <c r="O19" s="98" t="s">
         <v>136</v>
       </c>
-      <c r="P19" s="86">
+      <c r="P19" s="75">
         <v>3.1399999999999997E-2</v>
       </c>
-      <c r="Q19" s="64">
+      <c r="Q19" s="56">
         <f t="shared" si="2"/>
         <v>16.327999999999999</v>
       </c>
-      <c r="R19" s="58"/>
-      <c r="S19" s="59"/>
+      <c r="R19" s="50"/>
+      <c r="S19" s="51"/>
     </row>
     <row r="20" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -2706,55 +2720,55 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="82" t="s">
+      <c r="C20" s="71" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="52" t="s">
+      <c r="E20" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F20" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="G20" s="89" t="s">
+      <c r="G20" s="78" t="s">
         <v>165</v>
       </c>
-      <c r="H20" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I20" s="69" t="s">
+      <c r="H20" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I20" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="J20" s="51" t="s">
+      <c r="J20" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="K20" s="108" t="s">
+      <c r="K20" s="92" t="s">
         <v>162</v>
       </c>
-      <c r="L20" s="52">
+      <c r="L20" s="44">
         <v>3</v>
       </c>
-      <c r="M20" s="51">
+      <c r="M20" s="43">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="N20" s="69">
+      <c r="N20" s="61">
         <v>1510</v>
       </c>
-      <c r="O20" s="122" t="s">
+      <c r="O20" s="99" t="s">
         <v>136</v>
       </c>
-      <c r="P20" s="71">
+      <c r="P20" s="63">
         <v>6.6100000000000006E-2</v>
       </c>
-      <c r="Q20" s="63">
+      <c r="Q20" s="55">
         <f t="shared" si="2"/>
         <v>99.811000000000007</v>
       </c>
-      <c r="R20" s="53"/>
-      <c r="S20" s="60"/>
+      <c r="R20" s="45"/>
+      <c r="S20" s="52"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
@@ -2762,56 +2776,56 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="83" t="s">
+      <c r="C21" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="D21" s="55" t="s">
+      <c r="D21" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="56" t="s">
+      <c r="E21" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="55" t="s">
+      <c r="F21" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="G21" s="84" t="s">
-        <v>137</v>
-      </c>
-      <c r="H21" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="I21" s="106" t="s">
-        <v>137</v>
-      </c>
-      <c r="J21" s="85" t="s">
-        <v>137</v>
-      </c>
-      <c r="K21" s="107" t="s">
+      <c r="G21" s="73" t="s">
+        <v>137</v>
+      </c>
+      <c r="H21" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="I21" s="90" t="s">
+        <v>137</v>
+      </c>
+      <c r="J21" s="74" t="s">
+        <v>137</v>
+      </c>
+      <c r="K21" s="91" t="s">
         <v>162</v>
       </c>
-      <c r="L21" s="56">
+      <c r="L21" s="48">
         <v>3</v>
       </c>
-      <c r="M21" s="57">
+      <c r="M21" s="49">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="N21" s="84" t="s">
-        <v>137</v>
-      </c>
-      <c r="O21" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="P21" s="107" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q21" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="R21" s="90" t="s">
+      <c r="N21" s="73" t="s">
+        <v>137</v>
+      </c>
+      <c r="O21" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="P21" s="91" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q21" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="R21" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="S21" s="65"/>
+      <c r="S21" s="57"/>
     </row>
     <row r="22" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
@@ -2819,55 +2833,55 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="124" t="s">
         <v>155</v>
       </c>
-      <c r="D22" s="51" t="s">
+      <c r="D22" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="52" t="s">
+      <c r="E22" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="51" t="s">
+      <c r="F22" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="52" t="s">
+      <c r="G22" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="H22" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I22" s="69" t="s">
+      <c r="H22" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I22" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="J22" s="109" t="s">
+      <c r="J22" s="93" t="s">
         <v>144</v>
       </c>
-      <c r="K22" s="53" t="s">
+      <c r="K22" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="L22" s="52">
+      <c r="L22" s="44">
         <v>12</v>
       </c>
-      <c r="M22" s="51">
+      <c r="M22" s="43">
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
-      <c r="N22" s="69">
+      <c r="N22" s="61">
         <v>6100</v>
       </c>
-      <c r="O22" s="123" t="s">
+      <c r="O22" s="100" t="s">
         <v>136</v>
       </c>
-      <c r="P22" s="71">
+      <c r="P22" s="63">
         <v>1.5E-3</v>
       </c>
-      <c r="Q22" s="63">
+      <c r="Q22" s="55">
         <f t="shared" si="2"/>
         <v>9.15</v>
       </c>
-      <c r="R22" s="53"/>
-      <c r="S22" s="60"/>
+      <c r="R22" s="45"/>
+      <c r="S22" s="52"/>
     </row>
     <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -2875,53 +2889,53 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="80"/>
-      <c r="D23" s="55" t="s">
+      <c r="C23" s="125"/>
+      <c r="D23" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="56" t="s">
+      <c r="E23" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="55" t="s">
+      <c r="F23" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="G23" s="56" t="s">
+      <c r="G23" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="H23" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="I23" s="70" t="s">
+      <c r="H23" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="I23" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="J23" s="110" t="s">
+      <c r="J23" s="94" t="s">
         <v>145</v>
       </c>
-      <c r="K23" s="58" t="s">
+      <c r="K23" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="L23" s="56">
+      <c r="L23" s="48">
         <v>3</v>
       </c>
-      <c r="M23" s="57">
+      <c r="M23" s="49">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="N23" s="70">
+      <c r="N23" s="62">
         <v>1600</v>
       </c>
-      <c r="O23" s="124" t="s">
+      <c r="O23" s="101" t="s">
         <v>136</v>
       </c>
-      <c r="P23" s="86">
+      <c r="P23" s="75">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q23" s="64">
+      <c r="Q23" s="56">
         <f t="shared" si="2"/>
         <v>1.76</v>
       </c>
-      <c r="R23" s="58"/>
-      <c r="S23" s="59"/>
+      <c r="R23" s="50"/>
+      <c r="S23" s="51"/>
     </row>
     <row r="24" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
@@ -2929,53 +2943,53 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="80"/>
-      <c r="D24" s="51" t="s">
+      <c r="C24" s="125"/>
+      <c r="D24" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="52" t="s">
+      <c r="E24" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="51" t="s">
+      <c r="F24" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="G24" s="52" t="s">
+      <c r="G24" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="H24" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I24" s="69" t="s">
+      <c r="H24" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I24" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="J24" s="109" t="s">
+      <c r="J24" s="93" t="s">
         <v>146</v>
       </c>
-      <c r="K24" s="53" t="s">
+      <c r="K24" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="L24" s="52">
+      <c r="L24" s="44">
         <v>1</v>
       </c>
-      <c r="M24" s="51">
+      <c r="M24" s="43">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N24" s="69">
+      <c r="N24" s="61">
         <v>600</v>
       </c>
-      <c r="O24" s="125" t="s">
+      <c r="O24" s="102" t="s">
         <v>136</v>
       </c>
-      <c r="P24" s="71">
+      <c r="P24" s="63">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q24" s="63">
+      <c r="Q24" s="55">
         <f t="shared" si="2"/>
         <v>0.72</v>
       </c>
-      <c r="R24" s="53"/>
-      <c r="S24" s="60"/>
+      <c r="R24" s="45"/>
+      <c r="S24" s="52"/>
     </row>
     <row r="25" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -2983,53 +2997,53 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="80"/>
-      <c r="D25" s="55" t="s">
+      <c r="C25" s="125"/>
+      <c r="D25" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="56" t="s">
+      <c r="E25" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F25" s="55" t="s">
+      <c r="F25" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="G25" s="56" t="s">
+      <c r="G25" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="H25" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="I25" s="70" t="s">
+      <c r="H25" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="I25" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="J25" s="110" t="s">
+      <c r="J25" s="94" t="s">
         <v>147</v>
       </c>
-      <c r="K25" s="58" t="s">
+      <c r="K25" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="L25" s="56">
+      <c r="L25" s="48">
         <v>3</v>
       </c>
-      <c r="M25" s="57">
+      <c r="M25" s="49">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="N25" s="70">
+      <c r="N25" s="62">
         <v>1600</v>
       </c>
-      <c r="O25" s="124" t="s">
+      <c r="O25" s="101" t="s">
         <v>136</v>
       </c>
-      <c r="P25" s="86">
+      <c r="P25" s="75">
         <v>1E-3</v>
       </c>
-      <c r="Q25" s="64">
+      <c r="Q25" s="56">
         <f t="shared" si="2"/>
         <v>1.6</v>
       </c>
-      <c r="R25" s="58"/>
-      <c r="S25" s="59"/>
+      <c r="R25" s="50"/>
+      <c r="S25" s="51"/>
     </row>
     <row r="26" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
@@ -3037,53 +3051,53 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="80"/>
-      <c r="D26" s="51" t="s">
+      <c r="C26" s="125"/>
+      <c r="D26" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="52" t="s">
+      <c r="E26" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="51" t="s">
+      <c r="F26" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="G26" s="52" t="s">
+      <c r="G26" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="H26" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I26" s="69" t="s">
+      <c r="H26" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I26" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="J26" s="111" t="s">
+      <c r="J26" s="95" t="s">
         <v>148</v>
       </c>
-      <c r="K26" s="53" t="s">
+      <c r="K26" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="L26" s="52">
+      <c r="L26" s="44">
         <v>1</v>
       </c>
-      <c r="M26" s="51">
+      <c r="M26" s="43">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N26" s="69">
+      <c r="N26" s="61">
         <v>520</v>
       </c>
-      <c r="O26" s="123" t="s">
+      <c r="O26" s="100" t="s">
         <v>136</v>
       </c>
-      <c r="P26" s="71">
+      <c r="P26" s="63">
         <v>1.61E-2</v>
       </c>
-      <c r="Q26" s="63">
+      <c r="Q26" s="55">
         <f t="shared" si="2"/>
         <v>8.3719999999999999</v>
       </c>
-      <c r="R26" s="53"/>
-      <c r="S26" s="60"/>
+      <c r="R26" s="45"/>
+      <c r="S26" s="52"/>
     </row>
     <row r="27" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
@@ -3091,53 +3105,53 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="80"/>
-      <c r="D27" s="55" t="s">
+      <c r="C27" s="125"/>
+      <c r="D27" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="56" t="s">
+      <c r="E27" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="55" t="s">
+      <c r="F27" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="G27" s="56" t="s">
+      <c r="G27" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="H27" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="I27" s="70" t="s">
+      <c r="H27" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="I27" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="J27" s="110" t="s">
+      <c r="J27" s="94" t="s">
         <v>149</v>
       </c>
-      <c r="K27" s="58" t="s">
+      <c r="K27" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="L27" s="56">
+      <c r="L27" s="48">
         <v>2</v>
       </c>
-      <c r="M27" s="57">
+      <c r="M27" s="49">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N27" s="70">
+      <c r="N27" s="62">
         <v>1100</v>
       </c>
-      <c r="O27" s="126" t="s">
+      <c r="O27" s="103" t="s">
         <v>136</v>
       </c>
-      <c r="P27" s="86">
+      <c r="P27" s="75">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="Q27" s="64">
+      <c r="Q27" s="56">
         <f t="shared" si="2"/>
         <v>0.88</v>
       </c>
-      <c r="R27" s="58"/>
-      <c r="S27" s="59"/>
+      <c r="R27" s="50"/>
+      <c r="S27" s="51"/>
     </row>
     <row r="28" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
@@ -3145,53 +3159,53 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="81"/>
-      <c r="D28" s="51" t="s">
+      <c r="C28" s="126"/>
+      <c r="D28" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="52" t="s">
+      <c r="E28" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="51" t="s">
+      <c r="F28" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="G28" s="52" t="s">
+      <c r="G28" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I28" s="69" t="s">
+      <c r="H28" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I28" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="J28" s="109" t="s">
+      <c r="J28" s="93" t="s">
         <v>174</v>
       </c>
-      <c r="K28" s="53" t="s">
+      <c r="K28" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="L28" s="52">
+      <c r="L28" s="44">
         <v>1</v>
       </c>
-      <c r="M28" s="51">
+      <c r="M28" s="43">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N28" s="69">
+      <c r="N28" s="61">
         <v>600</v>
       </c>
-      <c r="O28" s="127" t="s">
+      <c r="O28" s="104" t="s">
         <v>136</v>
       </c>
-      <c r="P28" s="71">
+      <c r="P28" s="63">
         <v>1.4E-3</v>
       </c>
-      <c r="Q28" s="63">
+      <c r="Q28" s="55">
         <f t="shared" si="2"/>
         <v>0.84</v>
       </c>
-      <c r="R28" s="53"/>
-      <c r="S28" s="60"/>
+      <c r="R28" s="45"/>
+      <c r="S28" s="52"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
@@ -3199,56 +3213,56 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="83" t="s">
+      <c r="C29" s="72" t="s">
         <v>159</v>
       </c>
-      <c r="D29" s="55" t="s">
+      <c r="D29" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="E29" s="56" t="s">
+      <c r="E29" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="55" t="s">
+      <c r="F29" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="G29" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="H29" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="I29" s="106" t="s">
-        <v>137</v>
-      </c>
-      <c r="J29" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="K29" s="107" t="s">
-        <v>137</v>
-      </c>
-      <c r="L29" s="56">
+      <c r="G29" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="H29" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="I29" s="90" t="s">
+        <v>137</v>
+      </c>
+      <c r="J29" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="K29" s="91" t="s">
+        <v>137</v>
+      </c>
+      <c r="L29" s="48">
         <v>5</v>
       </c>
-      <c r="M29" s="57">
+      <c r="M29" s="49">
         <f t="shared" si="1"/>
         <v>2500</v>
       </c>
-      <c r="N29" s="106" t="s">
-        <v>137</v>
-      </c>
-      <c r="O29" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="P29" s="107" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q29" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="R29" s="90" t="s">
+      <c r="N29" s="90" t="s">
+        <v>137</v>
+      </c>
+      <c r="O29" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="P29" s="91" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q29" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="R29" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="S29" s="59"/>
+      <c r="S29" s="51"/>
     </row>
     <row r="30" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
@@ -3256,55 +3270,55 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="82" t="s">
+      <c r="C30" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="51" t="s">
+      <c r="D30" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="E30" s="52" t="s">
+      <c r="E30" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="51" t="s">
+      <c r="F30" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="G30" s="52" t="s">
+      <c r="G30" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="H30" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I30" s="69" t="s">
+      <c r="H30" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I30" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="J30" s="51" t="s">
+      <c r="J30" s="43" t="s">
         <v>169</v>
       </c>
-      <c r="K30" s="108" t="s">
+      <c r="K30" s="92" t="s">
         <v>162</v>
       </c>
-      <c r="L30" s="52">
+      <c r="L30" s="44">
         <v>1</v>
       </c>
-      <c r="M30" s="51">
+      <c r="M30" s="43">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N30" s="69">
+      <c r="N30" s="61">
         <v>510</v>
       </c>
-      <c r="O30" s="68" t="s">
+      <c r="O30" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="P30" s="71">
+      <c r="P30" s="63">
         <v>0.45989999999999998</v>
       </c>
-      <c r="Q30" s="63">
+      <c r="Q30" s="55">
         <f t="shared" si="2"/>
         <v>234.54899999999998</v>
       </c>
-      <c r="R30" s="53"/>
-      <c r="S30" s="60"/>
+      <c r="R30" s="45"/>
+      <c r="S30" s="52"/>
     </row>
     <row r="31" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
@@ -3312,45 +3326,52 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="80" t="s">
+      <c r="C31" s="125" t="s">
         <v>156</v>
       </c>
-      <c r="D31" s="55" t="s">
+      <c r="D31" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="56" t="s">
+      <c r="E31" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="F31" s="55"/>
-      <c r="G31" s="56" t="s">
+      <c r="F31" s="47"/>
+      <c r="G31" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="H31" s="55"/>
-      <c r="I31" s="70" t="s">
+      <c r="H31" s="47"/>
+      <c r="I31" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="J31" s="55"/>
-      <c r="K31" s="107" t="s">
-        <v>137</v>
-      </c>
-      <c r="L31" s="56">
+      <c r="J31" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="K31" s="91" t="s">
+        <v>137</v>
+      </c>
+      <c r="L31" s="48">
         <v>1</v>
       </c>
-      <c r="M31" s="57">
+      <c r="M31" s="49">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N31" s="70"/>
-      <c r="O31" s="55"/>
-      <c r="P31" s="86"/>
-      <c r="Q31" s="64">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R31" s="90" t="s">
-        <v>179</v>
-      </c>
-      <c r="S31" s="59"/>
+      <c r="N31" s="91" t="s">
+        <v>137</v>
+      </c>
+      <c r="O31" s="91" t="s">
+        <v>137</v>
+      </c>
+      <c r="P31" s="91" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q31" s="91" t="s">
+        <v>137</v>
+      </c>
+      <c r="R31" s="79" t="s">
+        <v>187</v>
+      </c>
+      <c r="S31" s="51"/>
     </row>
     <row r="32" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
@@ -3358,53 +3379,53 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="80"/>
-      <c r="D32" s="51" t="s">
+      <c r="C32" s="125"/>
+      <c r="D32" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="52" t="s">
+      <c r="E32" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="F32" s="91" t="s">
+      <c r="F32" s="80" t="s">
         <v>170</v>
       </c>
-      <c r="G32" s="52" t="s">
+      <c r="G32" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="H32" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I32" s="69" t="s">
+      <c r="H32" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I32" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="J32" s="51" t="s">
+      <c r="J32" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="K32" s="108" t="s">
+      <c r="K32" s="92" t="s">
         <v>162</v>
       </c>
-      <c r="L32" s="52">
+      <c r="L32" s="44">
         <v>1</v>
       </c>
-      <c r="M32" s="51">
+      <c r="M32" s="43">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N32" s="69">
+      <c r="N32" s="61">
         <v>505</v>
       </c>
-      <c r="O32" s="123" t="s">
+      <c r="O32" s="100" t="s">
         <v>136</v>
       </c>
-      <c r="P32" s="71">
+      <c r="P32" s="63">
         <v>0.3054</v>
       </c>
-      <c r="Q32" s="63">
+      <c r="Q32" s="55">
         <f t="shared" si="2"/>
         <v>154.227</v>
       </c>
-      <c r="R32" s="53"/>
-      <c r="S32" s="60"/>
+      <c r="R32" s="45"/>
+      <c r="S32" s="52"/>
     </row>
     <row r="33" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -3412,53 +3433,53 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="80"/>
-      <c r="D33" s="55" t="s">
+      <c r="C33" s="125"/>
+      <c r="D33" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="56" t="s">
+      <c r="E33" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="F33" s="92" t="s">
+      <c r="F33" s="81" t="s">
         <v>172</v>
       </c>
-      <c r="G33" s="56" t="s">
+      <c r="G33" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="H33" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="I33" s="70" t="s">
+      <c r="H33" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="I33" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="J33" s="55" t="s">
+      <c r="J33" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="K33" s="107" t="s">
-        <v>137</v>
-      </c>
-      <c r="L33" s="56">
+      <c r="K33" s="91" t="s">
+        <v>137</v>
+      </c>
+      <c r="L33" s="48">
         <v>1</v>
       </c>
-      <c r="M33" s="57">
+      <c r="M33" s="49">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N33" s="70">
+      <c r="N33" s="62">
         <v>505</v>
       </c>
-      <c r="O33" s="93" t="s">
+      <c r="O33" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="P33" s="86">
+      <c r="P33" s="75">
         <v>0.45450000000000002</v>
       </c>
-      <c r="Q33" s="64">
+      <c r="Q33" s="56">
         <f t="shared" si="2"/>
         <v>229.52250000000001</v>
       </c>
-      <c r="R33" s="58"/>
-      <c r="S33" s="59"/>
+      <c r="R33" s="50"/>
+      <c r="S33" s="51"/>
     </row>
     <row r="34" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -3466,45 +3487,51 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="80"/>
-      <c r="D34" s="51" t="s">
+      <c r="C34" s="125"/>
+      <c r="D34" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="52" t="s">
+      <c r="E34" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="51"/>
-      <c r="G34" s="52" t="s">
+      <c r="F34" s="43"/>
+      <c r="G34" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="H34" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I34" s="69" t="s">
+      <c r="H34" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I34" s="61" t="s">
         <v>108</v>
       </c>
-      <c r="J34" s="51"/>
-      <c r="K34" s="108" t="s">
+      <c r="J34" s="43"/>
+      <c r="K34" s="92" t="s">
         <v>162</v>
       </c>
-      <c r="L34" s="52">
+      <c r="L34" s="44">
         <v>1</v>
       </c>
-      <c r="M34" s="51">
+      <c r="M34" s="43">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N34" s="69"/>
-      <c r="O34" s="51"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="63">
+      <c r="N34" s="61">
+        <v>505</v>
+      </c>
+      <c r="O34" s="100" t="s">
+        <v>185</v>
+      </c>
+      <c r="P34" s="63">
+        <v>2.29</v>
+      </c>
+      <c r="Q34" s="55">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R34" s="95" t="s">
-        <v>179</v>
-      </c>
-      <c r="S34" s="60"/>
+        <v>1156.45</v>
+      </c>
+      <c r="R34" s="84" t="s">
+        <v>186</v>
+      </c>
+      <c r="S34" s="52"/>
     </row>
     <row r="35" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
@@ -3512,49 +3539,57 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="79" t="s">
+      <c r="C35" s="124" t="s">
         <v>158</v>
       </c>
-      <c r="D35" s="55" t="s">
+      <c r="D35" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="56" t="s">
+      <c r="E35" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="55" t="s">
+      <c r="F35" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="G35" s="84" t="s">
+      <c r="G35" s="73" t="s">
         <v>77</v>
       </c>
-      <c r="H35" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="I35" s="70" t="s">
+      <c r="H35" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="I35" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="J35" s="55"/>
-      <c r="K35" s="107" t="s">
-        <v>137</v>
-      </c>
-      <c r="L35" s="56">
+      <c r="J35" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K35" s="91" t="s">
+        <v>137</v>
+      </c>
+      <c r="L35" s="48">
         <v>1</v>
       </c>
-      <c r="M35" s="57">
+      <c r="M35" s="49">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N35" s="70"/>
-      <c r="O35" s="55"/>
-      <c r="P35" s="86"/>
-      <c r="Q35" s="64">
+      <c r="N35" s="62">
+        <v>505</v>
+      </c>
+      <c r="O35" s="130" t="s">
+        <v>185</v>
+      </c>
+      <c r="P35" s="75">
+        <v>0.9</v>
+      </c>
+      <c r="Q35" s="56">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R35" s="90" t="s">
-        <v>179</v>
-      </c>
-      <c r="S35" s="59"/>
+        <v>454.5</v>
+      </c>
+      <c r="R35" s="79" t="s">
+        <v>186</v>
+      </c>
+      <c r="S35" s="51"/>
     </row>
     <row r="36" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
@@ -3562,52 +3597,60 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="81"/>
-      <c r="D36" s="51" t="s">
+      <c r="C36" s="126"/>
+      <c r="D36" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="52" t="s">
+      <c r="E36" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="51" t="s">
+      <c r="F36" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="G36" s="52" t="s">
+      <c r="G36" s="78" t="s">
         <v>78</v>
       </c>
-      <c r="H36" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="I36" s="69" t="s">
+      <c r="H36" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="I36" s="61" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="112"/>
-      <c r="K36" s="108" t="s">
+      <c r="J36" s="131" t="s">
+        <v>183</v>
+      </c>
+      <c r="K36" s="92" t="s">
         <v>162</v>
       </c>
-      <c r="L36" s="52">
+      <c r="L36" s="44">
         <v>1</v>
       </c>
-      <c r="M36" s="51">
+      <c r="M36" s="43">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N36" s="69"/>
-      <c r="O36" s="112"/>
-      <c r="P36" s="71"/>
-      <c r="Q36" s="130">
+      <c r="N36" s="61">
+        <v>510</v>
+      </c>
+      <c r="O36" s="100" t="s">
+        <v>185</v>
+      </c>
+      <c r="P36" s="63">
+        <v>0.44</v>
+      </c>
+      <c r="Q36" s="105">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R36" s="95" t="s">
-        <v>179</v>
-      </c>
-      <c r="S36" s="61"/>
+        <v>224.4</v>
+      </c>
+      <c r="R36" s="84" t="s">
+        <v>186</v>
+      </c>
+      <c r="S36" s="53"/>
     </row>
     <row r="37" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="33"/>
-      <c r="C37" s="77"/>
+      <c r="C37" s="69"/>
       <c r="D37" s="34" t="s">
         <v>5</v>
       </c>
@@ -3616,26 +3659,26 @@
       <c r="G37" s="37"/>
       <c r="H37" s="37"/>
       <c r="I37" s="36"/>
-      <c r="J37" s="36"/>
+      <c r="J37" s="132"/>
       <c r="K37" s="37"/>
       <c r="L37" s="37"/>
       <c r="M37" s="37"/>
-      <c r="N37" s="96" t="s">
-        <v>180</v>
-      </c>
-      <c r="O37" s="97"/>
-      <c r="P37" s="97"/>
-      <c r="Q37" s="98">
+      <c r="N37" s="106" t="s">
+        <v>179</v>
+      </c>
+      <c r="O37" s="107"/>
+      <c r="P37" s="107"/>
+      <c r="Q37" s="85">
         <f>SUM(Q10:Q36)</f>
-        <v>1201.3024999999998</v>
-      </c>
-      <c r="R37" s="47"/>
-      <c r="S37" s="48"/>
+        <v>3036.6524999999997</v>
+      </c>
+      <c r="R37" s="120"/>
+      <c r="S37" s="121"/>
     </row>
     <row r="38" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="25"/>
-      <c r="C38" s="78"/>
+      <c r="C38" s="70"/>
       <c r="D38" s="9" t="s">
         <v>6</v>
       </c>
@@ -3648,35 +3691,30 @@
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
-      <c r="N38" s="96" t="s">
-        <v>181</v>
-      </c>
-      <c r="O38" s="97"/>
-      <c r="P38" s="99"/>
-      <c r="Q38" s="100">
+      <c r="N38" s="106" t="s">
+        <v>180</v>
+      </c>
+      <c r="O38" s="107"/>
+      <c r="P38" s="129"/>
+      <c r="Q38" s="86">
         <v>42.53</v>
       </c>
-      <c r="R38" s="49"/>
-      <c r="S38" s="50"/>
+      <c r="R38" s="122"/>
+      <c r="S38" s="123"/>
     </row>
     <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="N39" s="96" t="s">
-        <v>182</v>
-      </c>
-      <c r="O39" s="97"/>
-      <c r="P39" s="97"/>
-      <c r="Q39" s="101">
+      <c r="N39" s="106" t="s">
+        <v>181</v>
+      </c>
+      <c r="O39" s="107"/>
+      <c r="P39" s="107"/>
+      <c r="Q39" s="87">
         <f>Q37/500</f>
-        <v>2.4026049999999994</v>
+        <v>6.0733049999999995</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="N15:N16"/>
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
     <mergeCell ref="R37:S38"/>
@@ -3689,6 +3727,11 @@
     <mergeCell ref="O15:O16"/>
     <mergeCell ref="N37:P37"/>
     <mergeCell ref="N38:P38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="N15:N16"/>
   </mergeCells>
   <conditionalFormatting sqref="O11">
     <cfRule type="dataBar" priority="4">

--- a/Deliverables/Control_Board/BOM/Control_Board_BOM (500 Boards).xlsx
+++ b/Deliverables/Control_Board/BOM/Control_Board_BOM (500 Boards).xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Control_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ChristianRaun-EthercatDesign\Deliverables\Control_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370284ED-8F79-40EB-8105-287A2A756DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="189">
   <si>
     <t>Component list</t>
   </si>
@@ -589,9 +588,6 @@
     <t>---------</t>
   </si>
   <si>
-    <t xml:space="preserve">1x40 pins Header 5 PCS per Lot </t>
-  </si>
-  <si>
     <t>Custom Supplier</t>
   </si>
   <si>
@@ -599,12 +595,18 @@
   </si>
   <si>
     <t>Already Purchas From Client Side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 30 pins Header 10 PCS per Lot </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 40 pins Header 10 PCS per Lot </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1485,6 +1487,15 @@
     <xf numFmtId="165" fontId="18" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -1559,15 +1570,6 @@
     <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1613,7 +1615,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1909,7 +1911,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:S39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1945,15 +1947,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="117"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="120"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2003,7 +2005,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="118"/>
+      <c r="S3" s="121"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2028,7 +2030,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="119"/>
+      <c r="S4" s="122"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2053,7 +2055,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="119"/>
+      <c r="S5" s="122"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2074,7 +2076,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="119"/>
+      <c r="S6" s="122"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2095,7 +2097,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="119"/>
+      <c r="S7" s="122"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2116,7 +2118,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="119"/>
+      <c r="S8" s="122"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2181,7 +2183,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="124" t="s">
+      <c r="C10" s="127" t="s">
         <v>151</v>
       </c>
       <c r="D10" s="43" t="s">
@@ -2237,7 +2239,7 @@
         <f t="shared" ref="B11:B35" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="125"/>
+      <c r="C11" s="128"/>
       <c r="D11" s="47" t="s">
         <v>12</v>
       </c>
@@ -2291,7 +2293,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="125"/>
+      <c r="C12" s="128"/>
       <c r="D12" s="43" t="s">
         <v>13</v>
       </c>
@@ -2345,7 +2347,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="125"/>
+      <c r="C13" s="128"/>
       <c r="D13" s="47" t="s">
         <v>14</v>
       </c>
@@ -2399,7 +2401,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="125"/>
+      <c r="C14" s="128"/>
       <c r="D14" s="43" t="s">
         <v>15</v>
       </c>
@@ -2453,7 +2455,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="124" t="s">
+      <c r="C15" s="127" t="s">
         <v>152</v>
       </c>
       <c r="D15" s="47" t="s">
@@ -2487,21 +2489,21 @@
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N15" s="114">
-        <v>140</v>
-      </c>
-      <c r="O15" s="127" t="s">
+      <c r="N15" s="117">
+        <v>17</v>
+      </c>
+      <c r="O15" s="130" t="s">
         <v>175</v>
       </c>
-      <c r="P15" s="110">
-        <v>0.41</v>
-      </c>
-      <c r="Q15" s="112">
+      <c r="P15" s="113">
+        <v>4.9411764705882302</v>
+      </c>
+      <c r="Q15" s="115">
         <f t="shared" si="2"/>
-        <v>57.4</v>
-      </c>
-      <c r="R15" s="108" t="s">
-        <v>184</v>
+        <v>83.999999999999915</v>
+      </c>
+      <c r="R15" s="111" t="s">
+        <v>188</v>
       </c>
       <c r="S15" s="51"/>
     </row>
@@ -2511,7 +2513,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="125"/>
+      <c r="C16" s="128"/>
       <c r="D16" s="43" t="s">
         <v>17</v>
       </c>
@@ -2543,11 +2545,11 @@
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N16" s="115"/>
-      <c r="O16" s="128"/>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="113"/>
-      <c r="R16" s="109"/>
+      <c r="N16" s="118"/>
+      <c r="O16" s="131"/>
+      <c r="P16" s="114"/>
+      <c r="Q16" s="116"/>
+      <c r="R16" s="112"/>
       <c r="S16" s="52"/>
     </row>
     <row r="17" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2556,7 +2558,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="126"/>
+      <c r="C17" s="129"/>
       <c r="D17" s="47" t="s">
         <v>18</v>
       </c>
@@ -2589,19 +2591,21 @@
         <v>500</v>
       </c>
       <c r="N17" s="62">
-        <v>510</v>
+        <v>35</v>
       </c>
       <c r="O17" s="83" t="s">
         <v>175</v>
       </c>
       <c r="P17" s="75">
-        <v>0.13200000000000001</v>
+        <v>1.8846153846153799</v>
       </c>
       <c r="Q17" s="56">
         <f t="shared" si="2"/>
-        <v>67.320000000000007</v>
-      </c>
-      <c r="R17" s="50"/>
+        <v>65.961538461538296</v>
+      </c>
+      <c r="R17" s="50" t="s">
+        <v>187</v>
+      </c>
       <c r="S17" s="51"/>
     </row>
     <row r="18" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2610,7 +2614,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="124" t="s">
+      <c r="C18" s="127" t="s">
         <v>153</v>
       </c>
       <c r="D18" s="43" t="s">
@@ -2666,7 +2670,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="125"/>
+      <c r="C19" s="128"/>
       <c r="D19" s="47" t="s">
         <v>20</v>
       </c>
@@ -2833,7 +2837,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="124" t="s">
+      <c r="C22" s="127" t="s">
         <v>155</v>
       </c>
       <c r="D22" s="43" t="s">
@@ -2889,7 +2893,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="125"/>
+      <c r="C23" s="128"/>
       <c r="D23" s="47" t="s">
         <v>24</v>
       </c>
@@ -2943,7 +2947,7 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="125"/>
+      <c r="C24" s="128"/>
       <c r="D24" s="43" t="s">
         <v>25</v>
       </c>
@@ -2997,7 +3001,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="125"/>
+      <c r="C25" s="128"/>
       <c r="D25" s="47" t="s">
         <v>26</v>
       </c>
@@ -3051,7 +3055,7 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="125"/>
+      <c r="C26" s="128"/>
       <c r="D26" s="43" t="s">
         <v>27</v>
       </c>
@@ -3105,7 +3109,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="125"/>
+      <c r="C27" s="128"/>
       <c r="D27" s="47" t="s">
         <v>28</v>
       </c>
@@ -3159,7 +3163,7 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="126"/>
+      <c r="C28" s="129"/>
       <c r="D28" s="43" t="s">
         <v>29</v>
       </c>
@@ -3326,7 +3330,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="125" t="s">
+      <c r="C31" s="128" t="s">
         <v>156</v>
       </c>
       <c r="D31" s="47" t="s">
@@ -3369,7 +3373,7 @@
         <v>137</v>
       </c>
       <c r="R31" s="79" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S31" s="51"/>
     </row>
@@ -3379,7 +3383,7 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="125"/>
+      <c r="C32" s="128"/>
       <c r="D32" s="43" t="s">
         <v>33</v>
       </c>
@@ -3433,7 +3437,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="125"/>
+      <c r="C33" s="128"/>
       <c r="D33" s="47" t="s">
         <v>34</v>
       </c>
@@ -3487,7 +3491,7 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="125"/>
+      <c r="C34" s="128"/>
       <c r="D34" s="43" t="s">
         <v>35</v>
       </c>
@@ -3519,7 +3523,7 @@
         <v>505</v>
       </c>
       <c r="O34" s="100" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P34" s="63">
         <v>2.29</v>
@@ -3529,7 +3533,7 @@
         <v>1156.45</v>
       </c>
       <c r="R34" s="84" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S34" s="52"/>
     </row>
@@ -3539,7 +3543,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="124" t="s">
+      <c r="C35" s="127" t="s">
         <v>158</v>
       </c>
       <c r="D35" s="47" t="s">
@@ -3576,8 +3580,8 @@
       <c r="N35" s="62">
         <v>505</v>
       </c>
-      <c r="O35" s="130" t="s">
-        <v>185</v>
+      <c r="O35" s="106" t="s">
+        <v>184</v>
       </c>
       <c r="P35" s="75">
         <v>0.9</v>
@@ -3587,7 +3591,7 @@
         <v>454.5</v>
       </c>
       <c r="R35" s="79" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S35" s="51"/>
     </row>
@@ -3597,7 +3601,7 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="126"/>
+      <c r="C36" s="129"/>
       <c r="D36" s="43" t="s">
         <v>37</v>
       </c>
@@ -3616,7 +3620,7 @@
       <c r="I36" s="61" t="s">
         <v>110</v>
       </c>
-      <c r="J36" s="131" t="s">
+      <c r="J36" s="107" t="s">
         <v>183</v>
       </c>
       <c r="K36" s="92" t="s">
@@ -3633,7 +3637,7 @@
         <v>510</v>
       </c>
       <c r="O36" s="100" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P36" s="63">
         <v>0.44</v>
@@ -3643,7 +3647,7 @@
         <v>224.4</v>
       </c>
       <c r="R36" s="84" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S36" s="53"/>
     </row>
@@ -3659,21 +3663,21 @@
       <c r="G37" s="37"/>
       <c r="H37" s="37"/>
       <c r="I37" s="36"/>
-      <c r="J37" s="132"/>
+      <c r="J37" s="108"/>
       <c r="K37" s="37"/>
       <c r="L37" s="37"/>
       <c r="M37" s="37"/>
-      <c r="N37" s="106" t="s">
+      <c r="N37" s="109" t="s">
         <v>179</v>
       </c>
-      <c r="O37" s="107"/>
-      <c r="P37" s="107"/>
+      <c r="O37" s="110"/>
+      <c r="P37" s="110"/>
       <c r="Q37" s="85">
         <f>SUM(Q10:Q36)</f>
-        <v>3036.6524999999997</v>
-      </c>
-      <c r="R37" s="120"/>
-      <c r="S37" s="121"/>
+        <v>3061.8940384615385</v>
+      </c>
+      <c r="R37" s="123"/>
+      <c r="S37" s="124"/>
     </row>
     <row r="38" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
@@ -3691,26 +3695,26 @@
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
-      <c r="N38" s="106" t="s">
+      <c r="N38" s="109" t="s">
         <v>180</v>
       </c>
-      <c r="O38" s="107"/>
-      <c r="P38" s="129"/>
+      <c r="O38" s="110"/>
+      <c r="P38" s="132"/>
       <c r="Q38" s="86">
         <v>42.53</v>
       </c>
-      <c r="R38" s="122"/>
-      <c r="S38" s="123"/>
+      <c r="R38" s="125"/>
+      <c r="S38" s="126"/>
     </row>
     <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="N39" s="106" t="s">
+      <c r="N39" s="109" t="s">
         <v>181</v>
       </c>
-      <c r="O39" s="107"/>
-      <c r="P39" s="107"/>
+      <c r="O39" s="110"/>
+      <c r="P39" s="110"/>
       <c r="Q39" s="87">
         <f>Q37/500</f>
-        <v>6.0733049999999995</v>
+        <v>6.123788076923077</v>
       </c>
     </row>
   </sheetData>
@@ -3790,26 +3794,26 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="O11" r:id="rId1" xr:uid="{C6B02148-4707-4901-B984-AFB9EF721279}"/>
-    <hyperlink ref="O14" r:id="rId2" xr:uid="{4B274F78-A9B9-473A-B0C3-8DFFB2910F7C}"/>
-    <hyperlink ref="O13" r:id="rId3" xr:uid="{C3C8F532-EF15-46A7-B5C6-DF3ED28BEDAE}"/>
-    <hyperlink ref="O10" r:id="rId4" xr:uid="{E7F1D38A-F6D7-49DD-AD8F-7D617BEA4FCB}"/>
-    <hyperlink ref="O12" r:id="rId5" xr:uid="{153D22AA-0C97-4F93-B9D8-44560DC0DB9B}"/>
-    <hyperlink ref="O22" r:id="rId6" xr:uid="{67D82A06-0E26-4D8A-BA1B-AA0997884CA8}"/>
-    <hyperlink ref="O24" r:id="rId7" xr:uid="{B2F39CEB-7408-448F-ABCE-10BA8C0C084B}"/>
-    <hyperlink ref="O23" r:id="rId8" xr:uid="{90644E0C-D9D3-4FBB-A6C9-F044DF99AA2C}"/>
-    <hyperlink ref="O25" r:id="rId9" xr:uid="{E13DDD7B-527B-4035-A117-0E8A528BCBC7}"/>
-    <hyperlink ref="O26" r:id="rId10" xr:uid="{EC77F680-C5DA-4773-BCCB-88AB1718A489}"/>
-    <hyperlink ref="O27" r:id="rId11" xr:uid="{815A3342-7A81-4389-9B49-94BA3C68A3E2}"/>
-    <hyperlink ref="O18" r:id="rId12" xr:uid="{ED3D1B58-94F7-4EA1-856F-4F1130EAE950}"/>
-    <hyperlink ref="O19" r:id="rId13" xr:uid="{7D994EC4-7BD4-4415-A0BB-1A8F4726EB2A}"/>
-    <hyperlink ref="O20" r:id="rId14" xr:uid="{F2AA434C-E8FC-4109-B38C-E3A167DFB339}"/>
-    <hyperlink ref="O30" r:id="rId15" xr:uid="{F25C6ACA-5304-4BBB-89FE-5C2F70CBCA87}"/>
-    <hyperlink ref="O32" r:id="rId16" xr:uid="{F0CEC956-9CBD-4081-9E02-541B43334ECA}"/>
-    <hyperlink ref="O33" r:id="rId17" xr:uid="{3D961140-2712-4F5B-B3F7-1A596F78428B}"/>
-    <hyperlink ref="O28" r:id="rId18" xr:uid="{E075B427-64F6-4177-AF2A-7BBE421C14A7}"/>
-    <hyperlink ref="O17" r:id="rId19" xr:uid="{33DB0923-3B38-405A-BBDD-6664383AF100}"/>
-    <hyperlink ref="O15" r:id="rId20" xr:uid="{35CE2201-5F33-4F0C-A2FA-23C8E510FC0B}"/>
+    <hyperlink ref="O11" r:id="rId1"/>
+    <hyperlink ref="O14" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O10" r:id="rId4"/>
+    <hyperlink ref="O12" r:id="rId5"/>
+    <hyperlink ref="O22" r:id="rId6"/>
+    <hyperlink ref="O24" r:id="rId7"/>
+    <hyperlink ref="O23" r:id="rId8"/>
+    <hyperlink ref="O25" r:id="rId9"/>
+    <hyperlink ref="O26" r:id="rId10"/>
+    <hyperlink ref="O27" r:id="rId11"/>
+    <hyperlink ref="O18" r:id="rId12"/>
+    <hyperlink ref="O19" r:id="rId13"/>
+    <hyperlink ref="O20" r:id="rId14"/>
+    <hyperlink ref="O30" r:id="rId15"/>
+    <hyperlink ref="O32" r:id="rId16"/>
+    <hyperlink ref="O33" r:id="rId17"/>
+    <hyperlink ref="O28" r:id="rId18"/>
+    <hyperlink ref="O17" r:id="rId19"/>
+    <hyperlink ref="O15" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId21"/>

--- a/Deliverables/Control_Board/BOM/Control_Board_BOM (500 Boards).xlsx
+++ b/Deliverables/Control_Board/BOM/Control_Board_BOM (500 Boards).xlsx
@@ -1496,6 +1496,45 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -1504,72 +1543,33 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1615,7 +1615,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1947,15 +1947,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="120"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="110"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2005,7 +2005,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="121"/>
+      <c r="S3" s="111"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2030,7 +2030,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="122"/>
+      <c r="S4" s="112"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2055,7 +2055,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="122"/>
+      <c r="S5" s="112"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2076,7 +2076,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="122"/>
+      <c r="S6" s="112"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2097,7 +2097,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="122"/>
+      <c r="S7" s="112"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2118,7 +2118,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="122"/>
+      <c r="S8" s="112"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2183,7 +2183,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="127" t="s">
+      <c r="C10" s="117" t="s">
         <v>151</v>
       </c>
       <c r="D10" s="43" t="s">
@@ -2239,7 +2239,7 @@
         <f t="shared" ref="B11:B35" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="128"/>
+      <c r="C11" s="118"/>
       <c r="D11" s="47" t="s">
         <v>12</v>
       </c>
@@ -2293,7 +2293,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="128"/>
+      <c r="C12" s="118"/>
       <c r="D12" s="43" t="s">
         <v>13</v>
       </c>
@@ -2347,7 +2347,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="128"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="47" t="s">
         <v>14</v>
       </c>
@@ -2401,7 +2401,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="128"/>
+      <c r="C14" s="118"/>
       <c r="D14" s="43" t="s">
         <v>15</v>
       </c>
@@ -2455,7 +2455,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="127" t="s">
+      <c r="C15" s="117" t="s">
         <v>152</v>
       </c>
       <c r="D15" s="47" t="s">
@@ -2489,20 +2489,20 @@
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N15" s="117">
+      <c r="N15" s="129">
         <v>17</v>
       </c>
-      <c r="O15" s="130" t="s">
+      <c r="O15" s="120" t="s">
         <v>175</v>
       </c>
-      <c r="P15" s="113">
+      <c r="P15" s="125">
         <v>4.9411764705882302</v>
       </c>
-      <c r="Q15" s="115">
+      <c r="Q15" s="127">
         <f t="shared" si="2"/>
         <v>83.999999999999915</v>
       </c>
-      <c r="R15" s="111" t="s">
+      <c r="R15" s="131" t="s">
         <v>188</v>
       </c>
       <c r="S15" s="51"/>
@@ -2513,7 +2513,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="128"/>
+      <c r="C16" s="118"/>
       <c r="D16" s="43" t="s">
         <v>17</v>
       </c>
@@ -2545,11 +2545,11 @@
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N16" s="118"/>
-      <c r="O16" s="131"/>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="116"/>
-      <c r="R16" s="112"/>
+      <c r="N16" s="130"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="126"/>
+      <c r="Q16" s="128"/>
+      <c r="R16" s="132"/>
       <c r="S16" s="52"/>
     </row>
     <row r="17" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2558,7 +2558,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="129"/>
+      <c r="C17" s="119"/>
       <c r="D17" s="47" t="s">
         <v>18</v>
       </c>
@@ -2603,7 +2603,7 @@
         <f t="shared" si="2"/>
         <v>65.961538461538296</v>
       </c>
-      <c r="R17" s="50" t="s">
+      <c r="R17" s="79" t="s">
         <v>187</v>
       </c>
       <c r="S17" s="51"/>
@@ -2614,7 +2614,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="127" t="s">
+      <c r="C18" s="117" t="s">
         <v>153</v>
       </c>
       <c r="D18" s="43" t="s">
@@ -2670,7 +2670,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="128"/>
+      <c r="C19" s="118"/>
       <c r="D19" s="47" t="s">
         <v>20</v>
       </c>
@@ -2837,7 +2837,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="127" t="s">
+      <c r="C22" s="117" t="s">
         <v>155</v>
       </c>
       <c r="D22" s="43" t="s">
@@ -2893,7 +2893,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="128"/>
+      <c r="C23" s="118"/>
       <c r="D23" s="47" t="s">
         <v>24</v>
       </c>
@@ -2947,7 +2947,7 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="128"/>
+      <c r="C24" s="118"/>
       <c r="D24" s="43" t="s">
         <v>25</v>
       </c>
@@ -3001,7 +3001,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="128"/>
+      <c r="C25" s="118"/>
       <c r="D25" s="47" t="s">
         <v>26</v>
       </c>
@@ -3055,7 +3055,7 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="128"/>
+      <c r="C26" s="118"/>
       <c r="D26" s="43" t="s">
         <v>27</v>
       </c>
@@ -3109,7 +3109,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="128"/>
+      <c r="C27" s="118"/>
       <c r="D27" s="47" t="s">
         <v>28</v>
       </c>
@@ -3163,7 +3163,7 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="129"/>
+      <c r="C28" s="119"/>
       <c r="D28" s="43" t="s">
         <v>29</v>
       </c>
@@ -3330,7 +3330,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="128" t="s">
+      <c r="C31" s="118" t="s">
         <v>156</v>
       </c>
       <c r="D31" s="47" t="s">
@@ -3383,7 +3383,7 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="128"/>
+      <c r="C32" s="118"/>
       <c r="D32" s="43" t="s">
         <v>33</v>
       </c>
@@ -3437,7 +3437,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="128"/>
+      <c r="C33" s="118"/>
       <c r="D33" s="47" t="s">
         <v>34</v>
       </c>
@@ -3491,7 +3491,7 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="128"/>
+      <c r="C34" s="118"/>
       <c r="D34" s="43" t="s">
         <v>35</v>
       </c>
@@ -3543,7 +3543,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="127" t="s">
+      <c r="C35" s="117" t="s">
         <v>158</v>
       </c>
       <c r="D35" s="47" t="s">
@@ -3601,7 +3601,7 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="129"/>
+      <c r="C36" s="119"/>
       <c r="D36" s="43" t="s">
         <v>37</v>
       </c>
@@ -3667,17 +3667,17 @@
       <c r="K37" s="37"/>
       <c r="L37" s="37"/>
       <c r="M37" s="37"/>
-      <c r="N37" s="109" t="s">
+      <c r="N37" s="122" t="s">
         <v>179</v>
       </c>
-      <c r="O37" s="110"/>
-      <c r="P37" s="110"/>
+      <c r="O37" s="123"/>
+      <c r="P37" s="123"/>
       <c r="Q37" s="85">
         <f>SUM(Q10:Q36)</f>
         <v>3061.8940384615385</v>
       </c>
-      <c r="R37" s="123"/>
-      <c r="S37" s="124"/>
+      <c r="R37" s="113"/>
+      <c r="S37" s="114"/>
     </row>
     <row r="38" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
@@ -3695,30 +3695,35 @@
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
       <c r="M38" s="10"/>
-      <c r="N38" s="109" t="s">
+      <c r="N38" s="122" t="s">
         <v>180</v>
       </c>
-      <c r="O38" s="110"/>
-      <c r="P38" s="132"/>
+      <c r="O38" s="123"/>
+      <c r="P38" s="124"/>
       <c r="Q38" s="86">
-        <v>42.53</v>
-      </c>
-      <c r="R38" s="125"/>
-      <c r="S38" s="126"/>
+        <v>80.53</v>
+      </c>
+      <c r="R38" s="115"/>
+      <c r="S38" s="116"/>
     </row>
     <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="N39" s="109" t="s">
+      <c r="N39" s="122" t="s">
         <v>181</v>
       </c>
-      <c r="O39" s="110"/>
-      <c r="P39" s="110"/>
+      <c r="O39" s="123"/>
+      <c r="P39" s="123"/>
       <c r="Q39" s="87">
-        <f>Q37/500</f>
-        <v>6.123788076923077</v>
+        <f>SUM(Q37:Q38)/500</f>
+        <v>6.284848076923077</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="N15:N16"/>
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
     <mergeCell ref="R37:S38"/>
@@ -3731,11 +3736,6 @@
     <mergeCell ref="O15:O16"/>
     <mergeCell ref="N37:P37"/>
     <mergeCell ref="N38:P38"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="N15:N16"/>
   </mergeCells>
   <conditionalFormatting sqref="O11">
     <cfRule type="dataBar" priority="4">
